--- a/resultados/abatia/inventario_externos.xlsx
+++ b/resultados/abatia/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1221"/>
+  <dimension ref="A1:G1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38989,6 +38989,200 @@
         </is>
       </c>
     </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>https://chrome.google.com/webstore/detail/selection-reader-text-to/fdffijlhedcdiblbingmagmdnokokgbi?hl=pt-BR</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>chrome.google.com</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr"/>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/</t>
+        </is>
+      </c>
+      <c r="F1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:06:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>http://softwarepublico.gov.br/social/suite-vlibras</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>softwarepublico.gov.br</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr"/>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/</t>
+        </is>
+      </c>
+      <c r="F1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:06:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_Ato2011-2014/2011/Lei/L12527.htm</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>12.527/2011</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/menuCustomizavel?idAcao=50040</t>
+        </is>
+      </c>
+      <c r="F1224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:07:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>https://www.ingadigital.com.br/transparencia/index.php?sessao=3baba1b35eb23b</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>www.ingadigital.com.br</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr"/>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/menuCustomizavel?idAcao=50040</t>
+        </is>
+      </c>
+      <c r="F1225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:07:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>http://www.fnde.gov.br/sigefweb/index.php/liberacoes</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>www.fnde.gov.br</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>aqui.</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/menuCustomizavel?idAcao=50041</t>
+        </is>
+      </c>
+      <c r="F1226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:13:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>http://www1.tce.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>www1.tce.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr"/>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/menuCustomizavel/downloadDocumento?formulario.idAnexo=5</t>
+        </is>
+      </c>
+      <c r="F1227" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:27:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
